--- a/output/pdf_financials_xlsx/LGN.xlsx
+++ b/output/pdf_financials_xlsx/LGN.xlsx
@@ -2993,16 +2993,16 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000132</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.147</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.136</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.5669999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -3012,16 +3012,16 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000132</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.147</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.136</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.5669999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7526,7 +7526,11 @@
           <t>Lease payments [8]</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>-0.000132</v>
       </c>
@@ -8340,7 +8344,11 @@
           <t>Lease payments [9]</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LGN.xlsx
+++ b/output/pdf_financials_xlsx/LGN.xlsx
@@ -999,15 +999,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>0.039403</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-33.799</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>4.555</v>
@@ -2513,15 +2509,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.039403</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-33.799</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4.555</v>
@@ -7288,7 +7280,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -8008,7 +8004,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>0.039403</v>
       </c>
@@ -8628,7 +8628,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
